--- a/data/trans_orig/P16A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262583</t>
+          <t>261220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272131</t>
+          <t>272028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247525</t>
+          <t>246273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258659</t>
+          <t>258097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513374</t>
+          <t>514972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528503</t>
+          <t>528397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25544</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48715</t>
+          <t>48299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479591</t>
+          <t>479241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490130</t>
+          <t>490205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462738</t>
+          <t>464132</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483608</t>
+          <t>484798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948309</t>
+          <t>948725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971480</t>
+          <t>970094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314114</t>
+          <t>313621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327188</t>
+          <t>326971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334505</t>
+          <t>334501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644466</t>
+          <t>644643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653281</t>
+          <t>653284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347445</t>
+          <t>347560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357036</t>
+          <t>357668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352245</t>
+          <t>351273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365967</t>
+          <t>365576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>704672</t>
+          <t>704459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720963</t>
+          <t>721247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19745</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193427</t>
+          <t>193507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201571</t>
+          <t>201586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187923</t>
+          <t>187931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201717</t>
+          <t>201417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386652</t>
+          <t>386199</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401401</t>
+          <t>401860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262106</t>
+          <t>262913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269856</t>
+          <t>269858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264483</t>
+          <t>263828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275130</t>
+          <t>275117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531003</t>
+          <t>531076</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>544083</t>
+          <t>544085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35571</t>
+          <t>34586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>50553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592874</t>
+          <t>594118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>607768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602648</t>
+          <t>603633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>622500</t>
+          <t>622675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1203115</t>
+          <t>1202693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1227080</t>
+          <t>1227433</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>40818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63518</t>
+          <t>63909</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61241</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94346</t>
+          <t>96306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>702354</t>
+          <t>701959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724398</t>
+          <t>722716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719993</t>
+          <t>719602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>747024</t>
+          <t>748022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1431942</t>
+          <t>1429982</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1465047</t>
+          <t>1464272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>82874</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>164191</t>
+          <t>165057</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180172</t>
+          <t>176275</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>235616</t>
+          <t>233535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3194560</t>
+          <t>3192651</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3225005</t>
+          <t>3225338</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3215006</t>
+          <t>3214140</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3262425</t>
+          <t>3260836</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6419106</t>
+          <t>6421187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6474550</t>
+          <t>6478447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276182</t>
+          <t>276836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288511</t>
+          <t>288307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253943</t>
+          <t>253545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270040</t>
+          <t>269824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535971</t>
+          <t>537524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555458</t>
+          <t>556502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28472</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54099</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71884</t>
+          <t>68779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481256</t>
+          <t>480198</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500466</t>
+          <t>499522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468632</t>
+          <t>467654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494259</t>
+          <t>493659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956374</t>
+          <t>959479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>988385</t>
+          <t>990596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311973</t>
+          <t>312327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321170</t>
+          <t>321185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326014</t>
+          <t>325872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337816</t>
+          <t>337036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641082</t>
+          <t>642150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657072</t>
+          <t>656986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>40300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49090</t>
+          <t>49404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359587</t>
+          <t>360776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370965</t>
+          <t>370940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347740</t>
+          <t>347674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368184</t>
+          <t>368262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712866</t>
+          <t>712552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>735335</t>
+          <t>736136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>31363</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>56867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200026</t>
+          <t>201023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210622</t>
+          <t>210645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167850</t>
+          <t>168201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>191551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374725</t>
+          <t>375342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400383</t>
+          <t>400846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19157</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267871</t>
+          <t>267705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259983</t>
+          <t>260656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274330</t>
+          <t>274254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531061</t>
+          <t>532158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>546975</t>
+          <t>546951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645377</t>
+          <t>645494</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657860</t>
+          <t>658692</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>665314</t>
+          <t>664428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>683557</t>
+          <t>682520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316281</t>
+          <t>1315920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1338003</t>
+          <t>1338669</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35818</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48873</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79857</t>
+          <t>81532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68498</t>
+          <t>68625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106515</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740124</t>
+          <t>738309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>760937</t>
+          <t>760326</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>741663</t>
+          <t>739988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>772647</t>
+          <t>773401</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1490948</t>
+          <t>1490767</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1528965</t>
+          <t>1528838</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52781</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192835</t>
+          <t>196652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>254178</t>
+          <t>251511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>258055</t>
+          <t>263880</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>326046</t>
+          <t>331559</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3327918</t>
+          <t>3329318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3365160</t>
+          <t>3363721</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3290981</t>
+          <t>3293648</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3352324</t>
+          <t>3348507</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6637054</t>
+          <t>6631541</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6705045</t>
+          <t>6699220</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46573</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279542</t>
+          <t>278616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291151</t>
+          <t>291120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251792</t>
+          <t>251156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271722</t>
+          <t>272621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535891</t>
+          <t>535918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560800</t>
+          <t>559598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51406</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>66175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481325</t>
+          <t>479921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495559</t>
+          <t>495372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471678</t>
+          <t>473330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497901</t>
+          <t>497447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>960109</t>
+          <t>959484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>988326</t>
+          <t>987863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310858</t>
+          <t>310419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311908</t>
+          <t>311827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327344</t>
+          <t>327211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627589</t>
+          <t>627408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644337</t>
+          <t>644068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48971</t>
+          <t>49877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33349</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61384</t>
+          <t>60203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353684</t>
+          <t>354221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365702</t>
+          <t>365460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338312</t>
+          <t>337406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361269</t>
+          <t>360922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695863</t>
+          <t>697044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723898</t>
+          <t>724601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38379</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195401</t>
+          <t>195303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207501</t>
+          <t>208306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189740</t>
+          <t>189766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206426</t>
+          <t>207107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391429</t>
+          <t>390367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411494</t>
+          <t>412106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41977</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28637</t>
+          <t>28744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>54852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245575</t>
+          <t>246146</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257527</t>
+          <t>257734</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231138</t>
+          <t>230451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252875</t>
+          <t>252151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>483568</t>
+          <t>481386</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507601</t>
+          <t>507494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75318</t>
+          <t>74661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73784</t>
+          <t>72922</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114326</t>
+          <t>110214</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>610158</t>
+          <t>610563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634852</t>
+          <t>633530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>615976</t>
+          <t>616633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>648234</t>
+          <t>647272</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233526</t>
+          <t>1237638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1274068</t>
+          <t>1274930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60538</t>
+          <t>62144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>39766</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70827</t>
+          <t>70804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760983</t>
+          <t>762527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774657</t>
+          <t>774747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>765629</t>
+          <t>764023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>794351</t>
+          <t>793168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1533923</t>
+          <t>1533946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1565373</t>
+          <t>1564984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73728</t>
+          <t>71362</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112248</t>
+          <t>109099</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>234670</t>
+          <t>234505</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>297806</t>
+          <t>301382</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>318409</t>
+          <t>320372</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399037</t>
+          <t>396633</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3282102</t>
+          <t>3285251</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3320622</t>
+          <t>3322988</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3246736</t>
+          <t>3243160</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3309872</t>
+          <t>3310037</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6539855</t>
+          <t>6542259</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6620483</t>
+          <t>6618520</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>26088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>39920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294655</t>
+          <t>293083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305923</t>
+          <t>305540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>263547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275765</t>
+          <t>275634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561711</t>
+          <t>561157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578131</t>
+          <t>578112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>46046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>69955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69261</t>
+          <t>68646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102144</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478203</t>
+          <t>479612</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500778</t>
+          <t>500915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>443864</t>
+          <t>443770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467556</t>
+          <t>467679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928974</t>
+          <t>930917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>961857</t>
+          <t>962472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>47790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46465</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71898</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288171</t>
+          <t>288195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302985</t>
+          <t>303136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319765</t>
+          <t>319566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592790</t>
+          <t>596629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618223</t>
+          <t>619030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>49517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73275</t>
+          <t>72602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282164</t>
+          <t>282808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300842</t>
+          <t>300942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>425474</t>
+          <t>425870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>455039</t>
+          <t>454922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>714669</t>
+          <t>715342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749175</t>
+          <t>750022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167653</t>
+          <t>167716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175113</t>
+          <t>175165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179778</t>
+          <t>179842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191044</t>
+          <t>190937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>350542</t>
+          <t>350809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364283</t>
+          <t>364536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34872</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50781</t>
+          <t>51801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57089</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78773</t>
+          <t>78418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236936</t>
+          <t>236424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251285</t>
+          <t>251301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>206275</t>
+          <t>205255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222184</t>
+          <t>222537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>447919</t>
+          <t>448274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469603</t>
+          <t>470545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>23295</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51542</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113896</t>
+          <t>113283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>75264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142619</t>
+          <t>144968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572737</t>
+          <t>575122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599855</t>
+          <t>600984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>735048</t>
+          <t>735661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>817165</t>
+          <t>809733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1330604</t>
+          <t>1328255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1398685</t>
+          <t>1397959</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>42398</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82791</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115262</t>
+          <t>115117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>886443</t>
+          <t>886322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>917585</t>
+          <t>917022</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>632060</t>
+          <t>632494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>663527</t>
+          <t>663141</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1528310</t>
+          <t>1528455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590540</t>
+          <t>1590265</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>131136</t>
+          <t>129731</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196992</t>
+          <t>193911</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>304452</t>
+          <t>291033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>401918</t>
+          <t>399005</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>455011</t>
+          <t>459592</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>578475</t>
+          <t>580537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3261338</t>
+          <t>3264419</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3327194</t>
+          <t>3328599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3255463</t>
+          <t>3258376</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3352929</t>
+          <t>3366348</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6537237</t>
+          <t>6535175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6660701</t>
+          <t>6656120</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261220</t>
+          <t>262604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272028</t>
+          <t>272137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246273</t>
+          <t>246754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258097</t>
+          <t>258480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514972</t>
+          <t>514076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528397</t>
+          <t>528758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39817</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48299</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479241</t>
+          <t>479471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490205</t>
+          <t>490227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464132</t>
+          <t>463598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484798</t>
+          <t>484006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948725</t>
+          <t>949136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970094</t>
+          <t>972303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313621</t>
+          <t>314482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326971</t>
+          <t>326731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334501</t>
+          <t>334498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644643</t>
+          <t>644312</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653284</t>
+          <t>653266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25668</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347560</t>
+          <t>346671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357668</t>
+          <t>357051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351273</t>
+          <t>351997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365576</t>
+          <t>365757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>704459</t>
+          <t>703848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721247</t>
+          <t>721047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193507</t>
+          <t>193284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201586</t>
+          <t>201552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187931</t>
+          <t>187774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201417</t>
+          <t>201555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386199</t>
+          <t>386388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401860</t>
+          <t>401629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262913</t>
+          <t>262149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269858</t>
+          <t>269860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263828</t>
+          <t>264558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275117</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531076</t>
+          <t>531118</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>544085</t>
+          <t>543946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50553</t>
+          <t>49145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594118</t>
+          <t>595101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607768</t>
+          <t>608792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>603633</t>
+          <t>602148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>622675</t>
+          <t>622809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1202693</t>
+          <t>1204101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1227433</t>
+          <t>1227291</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40818</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63909</t>
+          <t>62810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96306</t>
+          <t>95329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>701959</t>
+          <t>702136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>722716</t>
+          <t>722926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719602</t>
+          <t>720701</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>748022</t>
+          <t>748322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1429982</t>
+          <t>1430959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1464272</t>
+          <t>1465778</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>82874</t>
+          <t>83533</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>118361</t>
+          <t>118772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165057</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>176275</t>
+          <t>180315</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>233535</t>
+          <t>234048</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3192651</t>
+          <t>3191992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3225338</t>
+          <t>3224183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3214140</t>
+          <t>3213707</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3260836</t>
+          <t>3260425</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6421187</t>
+          <t>6420674</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6478447</t>
+          <t>6474407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276836</t>
+          <t>276959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288307</t>
+          <t>288344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253545</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269824</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537524</t>
+          <t>537742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556502</t>
+          <t>556754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>55419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37662</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68779</t>
+          <t>70193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480198</t>
+          <t>481547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499522</t>
+          <t>500319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467654</t>
+          <t>467312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493659</t>
+          <t>493809</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959479</t>
+          <t>958065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990596</t>
+          <t>989009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312327</t>
+          <t>312004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321185</t>
+          <t>321171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325872</t>
+          <t>325408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337036</t>
+          <t>337203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642150</t>
+          <t>641234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656986</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49404</t>
+          <t>48733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360776</t>
+          <t>359853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370940</t>
+          <t>370933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347674</t>
+          <t>348482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368262</t>
+          <t>368330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712552</t>
+          <t>713223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736136</t>
+          <t>736562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51390</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56867</t>
+          <t>57415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201023</t>
+          <t>200920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210645</t>
+          <t>210590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168201</t>
+          <t>169638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191551</t>
+          <t>191979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375342</t>
+          <t>374794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400846</t>
+          <t>400313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20963</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267705</t>
+          <t>266209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260656</t>
+          <t>260583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274254</t>
+          <t>274784</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532158</t>
+          <t>532289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>546951</t>
+          <t>547027</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645494</t>
+          <t>645466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658692</t>
+          <t>658723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664428</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682520</t>
+          <t>682769</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315920</t>
+          <t>1316929</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1338669</t>
+          <t>1338717</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37633</t>
+          <t>35808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48753</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81532</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106696</t>
+          <t>107487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>738309</t>
+          <t>740134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>760326</t>
+          <t>761696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>739988</t>
+          <t>741404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773401</t>
+          <t>772767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1490767</t>
+          <t>1489976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>51830</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>89358</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>196652</t>
+          <t>196237</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>251511</t>
+          <t>252201</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>263880</t>
+          <t>260782</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>331559</t>
+          <t>331267</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3329318</t>
+          <t>3328583</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3363721</t>
+          <t>3366111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3293648</t>
+          <t>3292958</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3348507</t>
+          <t>3348922</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6631541</t>
+          <t>6631833</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6699220</t>
+          <t>6702318</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37547</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>46494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278616</t>
+          <t>278802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291120</t>
+          <t>290965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251156</t>
+          <t>250216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272621</t>
+          <t>271474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535918</t>
+          <t>535970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559598</t>
+          <t>561710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>49263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37796</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66175</t>
+          <t>64899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479921</t>
+          <t>479760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495372</t>
+          <t>494426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473330</t>
+          <t>473821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497447</t>
+          <t>498591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959484</t>
+          <t>960760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987863</t>
+          <t>988749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27466</t>
+          <t>27309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310419</t>
+          <t>311208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311827</t>
+          <t>311606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327211</t>
+          <t>327107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627408</t>
+          <t>627565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644068</t>
+          <t>644412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>26574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>50340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>60598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365460</t>
+          <t>365447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337406</t>
+          <t>336943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360922</t>
+          <t>360709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697044</t>
+          <t>696649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724601</t>
+          <t>723431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39441</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195303</t>
+          <t>196333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208306</t>
+          <t>208331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189766</t>
+          <t>190520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207107</t>
+          <t>206087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390367</t>
+          <t>391388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>412106</t>
+          <t>411254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54852</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246146</t>
+          <t>244477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257734</t>
+          <t>257630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230451</t>
+          <t>231423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252151</t>
+          <t>252754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481386</t>
+          <t>481078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507494</t>
+          <t>506871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>22245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>46383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74661</t>
+          <t>74984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>72550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110214</t>
+          <t>112813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>610563</t>
+          <t>610175</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>633530</t>
+          <t>634313</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>616633</t>
+          <t>616310</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>647272</t>
+          <t>646920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1237638</t>
+          <t>1235039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1274930</t>
+          <t>1275302</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62144</t>
+          <t>62252</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39766</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70804</t>
+          <t>71626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762527</t>
+          <t>761721</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774747</t>
+          <t>774697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>764023</t>
+          <t>763915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>793168</t>
+          <t>793624</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1533946</t>
+          <t>1533124</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1564984</t>
+          <t>1564443</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>113046</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>234505</t>
+          <t>237364</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>301382</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>320372</t>
+          <t>320580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>396633</t>
+          <t>395757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3285251</t>
+          <t>3281304</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3322988</t>
+          <t>3321764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3243160</t>
+          <t>3242484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3310037</t>
+          <t>3307178</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6542259</t>
+          <t>6543135</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6618520</t>
+          <t>6618312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>300820</t>
+          <t>307110</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293083</t>
+          <t>299980</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305540</t>
+          <t>312186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270066</t>
+          <t>296485</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263547</t>
+          <t>290886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275634</t>
+          <t>302457</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>570885</t>
+          <t>603595</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561157</t>
+          <t>594008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578112</t>
+          <t>610862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>41145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69955</t>
+          <t>72565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>83241</t>
+          <t>87057</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68646</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100201</t>
+          <t>103043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>492007</t>
+          <t>502410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479612</t>
+          <t>488515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500915</t>
+          <t>511954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>455870</t>
+          <t>485406</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>443770</t>
+          <t>472648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467679</t>
+          <t>496562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>947877</t>
+          <t>987816</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930917</t>
+          <t>971830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962472</t>
+          <t>1002912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,27 +11383,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>19798</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>27358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47790</t>
+          <t>48009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>58128</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45658</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -11496,22 +11496,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296944</t>
+          <t>295700</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288195</t>
+          <t>288140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303136</t>
+          <t>302374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311414</t>
+          <t>318051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301338</t>
+          <t>308372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319566</t>
+          <t>326602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>608358</t>
+          <t>613752</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>596629</t>
+          <t>601868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619030</t>
+          <t>625050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29749</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49517</t>
+          <t>51960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54520</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>47078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72602</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>293162</t>
+          <t>352342</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282808</t>
+          <t>340475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300942</t>
+          <t>360697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>440262</t>
+          <t>383488</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>425870</t>
+          <t>369670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>454922</t>
+          <t>392417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>733424</t>
+          <t>735830</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715342</t>
+          <t>718906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750022</t>
+          <t>747697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>30596</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36589</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172122</t>
+          <t>198807</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167716</t>
+          <t>193795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175165</t>
+          <t>202015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>203477</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179842</t>
+          <t>197260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190937</t>
+          <t>208554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>358313</t>
+          <t>402283</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>350809</t>
+          <t>394341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364536</t>
+          <t>408684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,17 +12447,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51801</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67144</t>
+          <t>67836</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56147</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78418</t>
+          <t>78143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>244872</t>
+          <t>246354</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236424</t>
+          <t>238156</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251301</t>
+          <t>252739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,17 +12560,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>214675</t>
+          <t>220267</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>205255</t>
+          <t>211416</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222537</t>
+          <t>227816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>459548</t>
+          <t>466621</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>448274</t>
+          <t>456314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>470545</t>
+          <t>476870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23295</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49157</t>
+          <t>56282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81358</t>
+          <t>96443</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113283</t>
+          <t>112455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>136327</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75264</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144968</t>
+          <t>159029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>589516</t>
+          <t>679803</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>575122</t>
+          <t>663405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600984</t>
+          <t>690787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>767586</t>
+          <t>674191</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>735661</t>
+          <t>658179</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>809733</t>
+          <t>689391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1357102</t>
+          <t>1353994</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1328255</t>
+          <t>1331292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1397959</t>
+          <t>1374345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848944</t>
+          <t>770634</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848944</t>
+          <t>770634</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848944</t>
+          <t>770634</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473223</t>
+          <t>1490321</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473223</t>
+          <t>1490321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473223</t>
+          <t>1490321</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42398</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>55700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82357</t>
+          <t>80554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>91068</t>
+          <t>98801</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>84032</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115117</t>
+          <t>116195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>901104</t>
+          <t>766981</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>886322</t>
+          <t>755699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>917022</t>
+          <t>775392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>651399</t>
+          <t>762296</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>632494</t>
+          <t>749452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>663141</t>
+          <t>774306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1552504</t>
+          <t>1529277</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1528455</t>
+          <t>1511883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590265</t>
+          <t>1544046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129731</t>
+          <t>158617</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>193911</t>
+          <t>210388</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>359919</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>291033</t>
+          <t>357335</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>399005</t>
+          <t>418483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>527702</t>
+          <t>569001</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>459592</t>
+          <t>529545</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>580537</t>
+          <t>610851</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3290547</t>
+          <t>3349509</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3264419</t>
+          <t>3320892</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3328599</t>
+          <t>3372663</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3297462</t>
+          <t>3343662</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3258376</t>
+          <t>3312408</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3366348</t>
+          <t>3373556</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6588010</t>
+          <t>6693169</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6535175</t>
+          <t>6651319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6656120</t>
+          <t>6732625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
